--- a/test-automation/EN301549v4.1.0-web-automation-matrix.en.xlsx
+++ b/test-automation/EN301549v4.1.0-web-automation-matrix.en.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\a11y-best-practices\test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBF082F-0FE2-42E3-96D8-C696B9C8030E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5624CC6-8317-454B-8DC6-CC90A5C3F5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4020" yWindow="-21600" windowWidth="26010" windowHeight="21705" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foreword" sheetId="1" r:id="rId1"/>
     <sheet name="Web test automation matrix" sheetId="2" r:id="rId2"/>
-    <sheet name="References" sheetId="19" r:id="rId3"/>
+    <sheet name="HdM Scale" sheetId="20" r:id="rId3"/>
+    <sheet name="References" sheetId="19" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Web test automation matrix'!$A$1:$F$1</definedName>
@@ -97,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="506">
   <si>
     <t>Deutsche Bezeichner v3.2.1</t>
   </si>
@@ -1574,7 +1575,50 @@
     <t>Kira Helen Frankenfeld. (2026, Juni 1). KI-gestützte multimodale Prüfmethoden zur automatisierten Barrierefreiheitsprüfung von Webseiten. https://nbn-resolving.org/urn:nbn:de:bsz:900-opus4-73472</t>
   </si>
   <si>
-    <t>Sabrina Berg. (2025, September 29). Large Language Model unterstützte Barrierefreiheitsprüfung für Websites—Analyse und proof of concept. https://nbn-resolving.org/urn:nbn:de:bsz:900-opus4-73046</t>
+    <t>Röhrle (2026)</t>
+  </si>
+  <si>
+    <t>Self-claim, deque (2026)</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>True positive, with correct location information</t>
+  </si>
+  <si>
+    <t>True positive, no or incorrect location information</t>
+  </si>
+  <si>
+    <t>False positive, with relevant location information</t>
+  </si>
+  <si>
+    <t>False positive, with no or irrelevant location information</t>
+  </si>
+  <si>
+    <t>Factor 0.5 for warnings (rather than errors)</t>
+  </si>
+  <si>
+    <t>In addition, the following relevant confusion matrix scores should be documented:</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>F1-Score</t>
+  </si>
+  <si>
+    <t>See Wikipedia (2026). Confusion Matrix</t>
+  </si>
+  <si>
+    <t>Sabrina Berg. (2025, September 29). Large Language Model unterstützte Barrierefreiheitsprüfung für Websites—Analyse und proof of concept. https://nbn-resolving.org/urn:nbn:de:bsz:900-opus4-73046
+ * 9.1.1.1: F1-Score=nn; Precision=…; Accuracy; HdM scale=</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1825,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1904,9 +1948,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2194,7 +2237,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>440</v>
       </c>
@@ -3794,7 +3837,9 @@
       <c r="D125" s="15"/>
       <c r="E125" s="14"/>
       <c r="F125" s="16"/>
-      <c r="H125" s="29"/>
+      <c r="H125" s="29" t="s">
+        <v>491</v>
+      </c>
       <c r="I125" s="12" t="s">
         <v>482</v>
       </c>
@@ -3802,7 +3847,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="126" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" s="20" customFormat="1" ht="57" x14ac:dyDescent="0.45">
       <c r="A126" s="15"/>
       <c r="B126" s="17" t="s">
         <v>219</v>
@@ -3811,6 +3856,9 @@
       <c r="D126" s="15"/>
       <c r="E126" s="14"/>
       <c r="F126" s="16"/>
+      <c r="H126" s="20" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="127" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A127" s="15"/>
@@ -6140,6 +6188,92 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D496424F-F927-4DEE-86F6-CA0EBBA8D988}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="48.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="42" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>-1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>-2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" s="43" t="s">
+        <v>504</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A13" r:id="rId1" display="Wikipedia (2026)" xr:uid="{D62AB9EB-D87E-47CE-A8F5-08F7E0C2AB4F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17C53C31-256B-4FBC-971D-951BAA2CE278}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -6147,18 +6281,18 @@
     <col min="1" max="1" width="98.9296875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="42" t="s">
-        <v>491</v>
+    <row r="1" spans="1:1" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A1" s="14" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="14" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="14" t="s">
         <v>489</v>
       </c>
     </row>
